--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486499_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486499_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6696</v>
+        <v>3.2593</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6677</v>
+        <v>4.1341</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9981</v>
+        <v>-0.8748</v>
       </c>
       <c r="G2" t="n">
         <v>-2.0617</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2539</v>
+        <v>0.8436</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2077</v>
+        <v>0.6742</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0461</v>
+        <v>0.1694</v>
       </c>
       <c r="V2" t="n">
         <v>3.3899</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6001</v>
+        <v>2.2804</v>
       </c>
       <c r="E3" t="n">
-        <v>3.686</v>
+        <v>2.7054</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0859</v>
+        <v>-0.425</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3012</v>
@@ -688,13 +688,13 @@
         <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1411</v>
+        <v>1.8215</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2953</v>
+        <v>1.3147</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8459</v>
+        <v>0.5068</v>
       </c>
       <c r="V3" t="n">
         <v>1.3252</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06560000000000001</v>
+        <v>1.1035</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1612</v>
+        <v>3.2607</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0955</v>
+        <v>-2.1572</v>
       </c>
       <c r="G4" t="n">
         <v>2.184</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1407</v>
+        <v>-0.1027</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3014</v>
+        <v>-0.2019</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1608</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7602</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1417</v>
+        <v>-0.3073</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1636</v>
+        <v>1.2754</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3053</v>
+        <v>-1.5827</v>
       </c>
       <c r="G5" t="n">
         <v>-0.241</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7295</v>
+        <v>0.5639</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3341</v>
+        <v>0.4458</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3955</v>
+        <v>0.1181</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2279</v>
+        <v>-0.351</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3436</v>
+        <v>-0.3125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1157</v>
+        <v>-0.0385</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2604</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4248</v>
+        <v>0.4521</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2776</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3287</v>
+        <v>0.1745</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5275</v>
+        <v>-1.8029</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0727</v>
+        <v>-0.3464</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6002</v>
+        <v>-1.4565</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.3786</v>
+        <v>-2.3142</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.2511</v>
+        <v>-1.5269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1275</v>
+        <v>-0.7873</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3519</v>
+        <v>0.4335</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9218</v>
+        <v>-0.5626</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5698</v>
+        <v>0.9961</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.0267</v>
+        <v>-2.7477</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3293</v>
+        <v>-0.9643</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6974</v>
+        <v>-1.7834</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2861</v>
+        <v>0.2938</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5997</v>
+        <v>0.5252</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3135</v>
+        <v>-0.2313</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6036</v>
+        <v>-1.9812</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0854</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5182</v>
+        <v>-2.5694</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3142</v>
+        <v>-4.3786</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5269</v>
+        <v>-3.2511</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7873</v>
+        <v>-1.1275</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4335</v>
+        <v>-0.3519</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5626</v>
+        <v>-1.9218</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9961</v>
+        <v>1.5698</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7477</v>
+        <v>-4.0267</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9643</v>
+        <v>-1.3293</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7834</v>
+        <v>-2.6974</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5069</v>
+        <v>0.8325</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2139</v>
+        <v>1.1152</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.293</v>
+        <v>-0.2827</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0724</v>
+        <v>-2.738</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3822</v>
+        <v>0.5625</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4546</v>
+        <v>-3.3005</v>
       </c>
       <c r="G9" t="n">
         <v>1.0063</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3563</v>
+        <v>0.6907</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4026</v>
+        <v>0.5828</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4112</v>
+        <v>-4.5536</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-1.294</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3212</v>
+        <v>-3.2596</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5146</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7776999999999999</v>
+        <v>-0.3647</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3447</v>
+        <v>0.1406</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5053</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6743</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0299</v>
+        <v>-4.6955</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6601</v>
+        <v>0.8404</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.69</v>
+        <v>-5.5359</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7597</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4452</v>
+        <v>-0.1109</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1286</v>
+        <v>0.3088</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5738</v>
+        <v>-0.4197</v>
       </c>
       <c r="V11" t="n">
         <v>-1.695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3959</v>
+        <v>-7.2773</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0665</v>
+        <v>-4.8862</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3294</v>
+        <v>-2.3911</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5773</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3836</v>
+        <v>-0.265</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0769</v>
+        <v>0.1034</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3067</v>
+        <v>-0.3683</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7105</v>
+        <v>-7.3518</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.482</v>
+        <v>-7.4315</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2285</v>
+        <v>0.0798</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2372</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3629</v>
+        <v>-0.0042</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2572</v>
+        <v>0.3076</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6201</v>
+        <v>-0.3118</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1952</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.7853</v>
+        <v>-24.4154</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2739</v>
+        <v>-0.9038999999999993</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.5112</v>
+        <v>-23.5114</v>
       </c>
       <c r="G14" t="n">
         <v>-22.4556</v>
@@ -1546,13 +1546,13 @@
         <v>11.9627</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2805</v>
+        <v>4.6506</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2242</v>
+        <v>5.593999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9433999999999998</v>
+        <v>-0.9434</v>
       </c>
       <c r="V14" t="n">
         <v>-2.2599</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.0314</v>
+        <v>7.8226</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2745</v>
+        <v>5.7506</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7569</v>
+        <v>2.0719</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1478</v>
+        <v>6.2393</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8218</v>
+        <v>1.7578</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3261</v>
+        <v>4.4815</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3775</v>
+        <v>5.5151</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7765</v>
+        <v>1.8432</v>
       </c>
       <c r="L15" t="n">
-        <v>2.601</v>
+        <v>3.6719</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7704</v>
+        <v>0.7242</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0452</v>
+        <v>-0.0854</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7251</v>
+        <v>0.8096</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8276</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2311</v>
+        <v>-0.5918</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9421</v>
+        <v>0.2355</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7111</v>
+        <v>-0.8274</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5374</v>
+        <v>7.7425</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5271</v>
+        <v>7.7419</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0103</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2393</v>
+        <v>6.752</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7578</v>
+        <v>2.4848</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4815</v>
+        <v>4.2672</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5151</v>
+        <v>6.2685</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8432</v>
+        <v>2.324</v>
       </c>
       <c r="L16" t="n">
-        <v>3.6719</v>
+        <v>3.9445</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7242</v>
+        <v>0.4835</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0854</v>
+        <v>0.1608</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8096</v>
+        <v>0.3227</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.877</v>
+        <v>-1.8344</v>
       </c>
       <c r="T16" t="n">
-        <v>0.012</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.889</v>
+        <v>-1.7455</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.9549</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.9407</v>
+        <v>7.1451</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0318</v>
+        <v>5.604</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9089</v>
+        <v>1.5412</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8734</v>
+        <v>5.1478</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7141</v>
+        <v>1.8218</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1594</v>
+        <v>3.3261</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2026</v>
+        <v>4.3775</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0878</v>
+        <v>1.7765</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1147</v>
+        <v>2.601</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6708</v>
+        <v>0.7704</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6262</v>
+        <v>0.0452</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0446</v>
+        <v>0.7251</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>2.8276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7177</v>
+        <v>-0.6552</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4817</v>
+        <v>0.2716</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.764</v>
+        <v>-0.9268</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.2599</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9554</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.864</v>
+        <v>5.773</v>
       </c>
       <c r="E18" t="n">
-        <v>7.2949</v>
+        <v>4.8024</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4309</v>
+        <v>0.9705</v>
       </c>
       <c r="G18" t="n">
-        <v>6.752</v>
+        <v>4.8734</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4848</v>
+        <v>4.7141</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2672</v>
+        <v>0.1594</v>
       </c>
       <c r="J18" t="n">
-        <v>6.2685</v>
+        <v>4.2026</v>
       </c>
       <c r="K18" t="n">
-        <v>2.324</v>
+        <v>4.0878</v>
       </c>
       <c r="L18" t="n">
-        <v>3.9445</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4835</v>
+        <v>0.6708</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1608</v>
+        <v>0.6262</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3227</v>
+        <v>0.0446</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.713</v>
+        <v>-0.45</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.536</v>
+        <v>0.2524</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.177</v>
+        <v>-0.7024</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8249</v>
+        <v>-0.3904</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9549</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0179</v>
+        <v>3.7925</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2516</v>
+        <v>4.8104</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2336</v>
+        <v>-1.0179</v>
       </c>
       <c r="G19" t="n">
         <v>2.0835</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.2539</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1262</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1643</v>
+        <v>0.38</v>
       </c>
       <c r="V19" t="n">
         <v>1.8902</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2905</v>
+        <v>0.5159</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2347</v>
+        <v>-0.7935</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5252</v>
+        <v>1.3094</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9819</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2501</v>
+        <v>0.4756</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0911</v>
+        <v>0.5324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.159</v>
+        <v>-0.0568</v>
       </c>
       <c r="V20" t="n">
         <v>0.3698</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5843</v>
+        <v>-0.1373</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7297</v>
+        <v>1.1767</v>
       </c>
       <c r="F21" t="n">
         <v>-1.314</v>
@@ -2092,10 +2092,10 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7006</v>
+        <v>-0.2536</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3305</v>
+        <v>0.1166</v>
       </c>
       <c r="U21" t="n">
         <v>-0.3701</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9674</v>
+        <v>-1.7208</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0673</v>
+        <v>-0.8207</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7893</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1781</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>0.0036</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1817</v>
+        <v>0.0649</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.144</v>
+        <v>-2.352</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6891</v>
+        <v>-0.4656</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4549</v>
+        <v>-1.8865</v>
       </c>
       <c r="G23" t="n">
         <v>0.9413</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5667</v>
+        <v>0.3587</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2139</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7806</v>
+        <v>0.3491</v>
       </c>
       <c r="V23" t="n">
         <v>-2.9995</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.201</v>
+        <v>-2.7964</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7745</v>
+        <v>-4.2157</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5735</v>
+        <v>1.4194</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1441</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0569</v>
+        <v>-0.6522</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.822</v>
+        <v>-0.2632</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2349</v>
+        <v>-0.3891</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>25.7852</v>
+        <v>25.7851</v>
       </c>
       <c r="E25" t="n">
-        <v>23.5112</v>
+        <v>23.5111</v>
       </c>
       <c r="F25" t="n">
-        <v>2.274099999999999</v>
+        <v>2.273899999999998</v>
       </c>
       <c r="G25" t="n">
         <v>22.4558</v>
@@ -2389,7 +2389,7 @@
         <v>-0.3640000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8790999999999999</v>
+        <v>0.8791</v>
       </c>
       <c r="O25" t="n">
         <v>-1.2433</v>
@@ -2404,13 +2404,13 @@
         <v>16.313</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.2807</v>
+        <v>-3.2805</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9430999999999999</v>
+        <v>0.9434000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.2239</v>
+        <v>-4.2241</v>
       </c>
       <c r="V25" t="n">
         <v>2.26</v>
